--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -83,6 +93,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -564,6 +578,49 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>510580</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>易方达中证500ETF</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>3.914</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>391.4</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>788.8</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>216.2</v>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>弹性股数法，滚存216.20元</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -660,25 +717,41 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>周一</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>500</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>待执行</t>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>✅已完成</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>3.914</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>弹性股数法，滚存216.20元</t>
         </is>
       </c>
     </row>

--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEAF1"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,6 +102,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -621,6 +629,49 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>510580</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>易方达中证500ETF</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4.262</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>426.2</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1220</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>第3期定投</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -774,7 +825,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>待执行</t>
+          <t>✅已完成</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>4.262</v>
+      </c>
+      <c r="H4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>第3期定投</t>
         </is>
       </c>
     </row>

--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="510580_买入记录" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="510580_定投日历" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="510300_买入记录" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="510300_定投日历" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1239,4 +1241,136 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>标的代码</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>标的名称</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>买入价格</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>买入份额</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>实际花费</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>手续费</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>累计投入</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>累计份额</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>累计滚存</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>期数</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>计划日期</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>星期</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>计划金额</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>实际日期</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>实际价格</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>实际份额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -1249,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,6 +1306,49 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>沪深300ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.8395</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>58074</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>58074</v>
+      </c>
+      <c r="I2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>原有持仓·一次性投入建仓，不参与微笑曲线计算</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,6 +1413,489 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>500</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>500</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>500</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>500</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>500</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>500</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>500</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2027-02-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>500</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2027-02-15</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>500</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>500</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2027-03-15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>500</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2027-03-29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>500</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2027-04-12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>500</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2027-04-26</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>500</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2027-05-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>500</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2027-05-24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>500</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2027-06-07</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>500</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
